--- a/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-1 氧化反應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下2-1 氧化反應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物質與氧結合的反應是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>生鏽</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>水加速氧化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>劇烈氧化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>氧化反應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>與氧</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>氧化後生成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>緩慢</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>氧化物</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>水加速氧化</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>燃點</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>產物</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>燃燒屬於哪種氧化？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>劇烈氧化</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氧氣與水</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>油漆隔絕氧</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>放光熱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>生鏽屬於哪種氧化？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>劇烈氧化</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>生鏽</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>緩慢氧化</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>慢</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>鎂與氧反應生成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>氧化鎂</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>一氧化碳CO</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>燃點</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>氧氣與水</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>MgO</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>防止生鏽可以？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>一氧化碳CO</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>油漆隔絕氧</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>更劇烈</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>防鏽</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>食物腐敗是哪種氧化？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>緩慢氧化</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>劇烈氧化</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>油漆隔絕氧</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>慢</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>燃燒需達到什麼溫度？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>緩慢氧化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>強白光</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>燃點</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>著火點</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>鐵長期在潮濕空氣會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>生鏽</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>燃點</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>緩慢</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氧化鎂</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>緩慢氧化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>氧化反應中物質與什麼結合？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>油漆隔絕氧</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>氧</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>緩慢</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>與氧</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-1 氧化反應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下2-1 氧化反應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鐵生鏽後質量如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>緩慢氧化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>一氧化碳CO</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>增加</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>結合氧</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>呼吸作用是氧化嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>隔絕氧減緩氧化</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>速率與是否放光</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>鋅較活潑先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>是(緩慢氧化)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>耗氧</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>碳燃燒充分生成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>劇烈氧化</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>緩慢</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>CO₂</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>切蘋果變褐色是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>氧化</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>酵素氧化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>油漆防鏽原理？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>隔絕氧氣水分</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>燃點</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>氧化鎂</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>阻隔</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>劇烈與緩慢氧化差在？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>鹼性(金屬氧化物)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>鋅較活潑先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>隔絕氧減緩氧化</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>速率與是否放光</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>快慢</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>鐵生鏽需要什麼條件？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>水加速氧化</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>氧氣與水</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>緩慢氧化</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>生鏽</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>氧化鎂是酸性還鹼性氧化物？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>減少水分延緩氧化</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>速率與是否放光</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>隔絕氧減緩氧化</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>鹼性(金屬氧化物)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>鎂在空氣中燃燒發出？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>緩慢氧化</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>強白光</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>生鏽</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>劇烈氧化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>鐵生鏽是快速還緩慢氧化？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>氧化鎂</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>緩慢</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>慢</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-1 氧化反應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下2-1 氧化反應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>鐵生鏽和鎂燃燒同為氧化差在？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>鋅較活潑先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>速率不同,一緩慢一劇烈</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>速率與是否放光</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>越活潑越易氧化</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>快慢</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何潮濕環境鐵易生鏽？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>水加速氧化</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>更劇烈</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>鍍鋅鐵皮刮傷仍防鏽因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>越活潑越易氧化</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>鋅較活潑先氧化保護鐵</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>速率不同,一緩慢一劇烈</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>鹼性(金屬氧化物)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>犧牲保護</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>碳不完全燃燒生成什麼有毒氣體？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>生鏽</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>強白光</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>一氧化碳CO</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>危害</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>食物用真空包裝防腐因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>速率與是否放光</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>隔絕氧減緩氧化</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>減少水分延緩氧化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>越活潑越易氧化</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>防氧化</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>金屬活性大小如何影響氧化難易？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>越活潑越易氧化</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>速率不同一劇烈一緩慢</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>鹼性(金屬氧化物)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>減少水分延緩氧化</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>活性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>乾燥劑放餅乾袋為何防潮？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>速率不同,一緩慢一劇烈</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>是(緩慢氧化)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>速率與是否放光</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>減少水分延緩氧化</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>防潮</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>鐵絨在純氧中燃燒比空氣中？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>強白光</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>隔絕氧氣水分</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>更劇烈</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>劇烈氧化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>氧濃度高</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何食物抽真空可延緩腐敗？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>隔絕氧減緩氧化</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>鋅較活潑先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>是(緩慢氧化)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>鹼性(金屬氧化物)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>防氧化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>燃燒與生鏽都是氧化的差別？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>隔絕氧減緩氧化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>鹼性(金屬氧化物)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>速率不同一劇烈一緩慢</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>鋅較活潑先氧化保護鐵</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>快慢</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>與氧</t>
+          <t>與氧：只要一種物質和氧氣發生反應結合在一起，這個反應就叫做氧化反應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>產物</t>
+          <t>產物：物質和氧結合之後產生的新物質，就叫做氧化物</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>放光熱</t>
+          <t>放光熱：燃燒是在很短時間內快速和氧結合，同時放出強烈的光和熱，屬於劇烈氧化</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>慢：生鏽是鐵和氧慢慢結合的過程，速度很慢，不會有明顯的光和熱，屬於緩慢氧化</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>MgO</t>
+          <t>MgO：鎂燃燒時和氧氣結合，產生的新物質就是氧化鎂，化學式寫作MgO</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防鏽</t>
+          <t>防鏽：在鐵的表面塗上油漆，可以把鐵和空氣中的氧氣隔開，就不容易生鏽了</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>慢：食物腐敗是食物中的成分慢慢與氧結合分解的過程，屬於緩慢氧化</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>著火點</t>
+          <t>著火點：物質要溫度達到某個特定的高溫（燃點）才會開始猛烈燃燒起來</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>緩慢氧化</t>
+          <t>緩慢氧化：鐵長期暴露在潮濕空氣中，會和氧氣、水分緩慢反應生成鐵鏽，這是一種緩慢氧化的現象</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>與氧</t>
+          <t>與氧：氧化反應最基本的定義是物質與氧結合，生成含氧的新物質</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>結合氧</t>
+          <t>結合氧：鐵生鏽是因為鐵原子和空氣中的氧原子結合，多了氧原子的重量，所以質量會增加</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>耗氧</t>
+          <t>耗氧：呼吸作用是身體把養分和吸進來的氧氣慢慢反應產生能量，屬於一種緩慢氧化</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>CO₂</t>
+          <t>CO₂：碳如果有足夠的氧氣可以完全燃燒，會生成二氧化碳這個氣體</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>酵素氧化</t>
+          <t>酵素氧化：蘋果切開後果肉中的成分接觸到空氣中的氧，被酵素催化發生氧化反應而變成褐色</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>阻隔</t>
+          <t>阻隔：油漆形成一層保護膜，把鐵和造成生鏽的氧氣、水分隔開，減緩生鏽速度</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>快慢：劇烈氧化像燃燒一樣反應很快又會發光發熱，緩慢氧化則反應慢且不會發光</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者：鐵要同時接觸到空氣中的氧氣和水分，才會逐漸生鏽，缺一不可</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>分類：金屬和氧結合形成的氧化物大多屬於鹼性氧化物，鎂是金屬所以氧化鎂是鹼性的</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>劇烈氧化</t>
+          <t>劇烈氧化：鎂燃燒是一種劇烈氧化反應，反應速度快、瞬間釋放大量能量，因此會發出耀眼的強白光</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>慢：鐵生鏽的過程進行得很慢，需要長時間持續與氧氣、水分接觸才會明顯，屬於緩慢氧化</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>快慢：兩者都是與氧結合的氧化反應，只是鐵生鏽反應很慢，鎂燃燒反應非常快速劇烈</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：水分會幫助氧氣和鐵之間進行反應，加快生鏽的速度，所以潮濕環境更容易生鏽</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>犧牲保護</t>
+          <t>犧牲保護：鋅比鐵更容易和氧反應，就算鍍層刮傷，鋅還是會搶先氧化，替裡面的鐵擋下腐蝕</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>危害</t>
+          <t>危害：碳在氧氣不夠的情況下燃燒不完全，會產生對人體有毒的一氧化碳氣體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>防氧化</t>
+          <t>防氧化：真空包裝把空氣抽掉，讓食物接觸不到氧氣，就能減緩食物氧化腐敗的速度</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>活性</t>
+          <t>活性：活性越大的金屬，代表它越容易和氧氣或其他物質發生反應，所以越容易被氧化</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>防潮</t>
+          <t>防潮：乾燥劑會吸收袋子裡的水分，讓餅乾接觸不到水，可以延緩氧化和變質的速度</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>氧濃度高</t>
+          <t>氧濃度高：純氧裡的氧氣濃度比一般空氣高很多，鐵絨能接觸到更多氧分子，燃燒反應就更劇烈</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>防氧化</t>
+          <t>防氧化：食物的腐敗變質常和氧化作用及微生物利用氧氣生長有關，抽真空能隔絕氧氣，減緩氧化反應和微生物活動，延長食物保存期限</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>快慢：燃燒和生鏽本質上都是物質與氧結合的氧化反應，主要差別在於反應速率不同，燃燒進行得又快又劇烈，生鏽則進行得緩慢</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-1_三種難度測驗卷.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>生鏽</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>水加速氧化</t>
+          <t>更劇烈</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>劇烈氧化</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>水加速氧化</t>
+          <t>增加</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>燃點</t>
+          <t>一氧化碳CO</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>氧氣與水</t>
+          <t>二氧化碳</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>油漆隔絕氧</t>
+          <t>緩慢氧化</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>水加速氧化</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氧化反應</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>劇烈氧化</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>氧化</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>生鏽</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>一氧化碳CO</t>
+          <t>緩慢</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>燃點</t>
+          <t>氧化反應</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>氧氣與水</t>
+          <t>生鏽</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>一氧化碳CO</t>
+          <t>生鏽</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>氧化物</t>
+          <t>氧化鎂</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>更劇烈</t>
+          <t>劇烈氧化</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>增加</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>劇烈氧化</t>
+          <t>水加速氧化</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>油漆隔絕氧</t>
+          <t>更劇烈</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>生鏽</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>油漆隔絕氧</t>
+          <t>更劇烈</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>強白光</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>劇烈氧化</t>
+          <t>燃點</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>氧化反應</t>
+          <t>氧氣與水</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>增加</t>
+          <t>生鏽</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>氧化</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>燃點</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>氧化鎂</t>
+          <t>一氧化碳CO</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>水加速氧化</t>
+          <t>氧化鎂</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>強白光</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>緩慢氧化</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>生鏽</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>水加速氧化</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>氧化反應</t>
+          <t>更劇烈</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>增加</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>更劇烈</t>
+          <t>油漆隔絕氧</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>氧化反應</t>
+          <t>劇烈氧化</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>生鏽</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>強白光</t>
-        </is>
-      </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>氧氣與水</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
